--- a/6.1 Myrmidon disturbance/output/yearly_population_growth_param_0.5.xlsx
+++ b/6.1 Myrmidon disturbance/output/yearly_population_growth_param_0.5.xlsx
@@ -776,13 +776,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>59621</v>
+        <v>57133</v>
       </c>
       <c r="C2" t="n">
-        <v>748</v>
+        <v>960</v>
       </c>
       <c r="D2" t="n">
-        <v>83975</v>
+        <v>99659</v>
       </c>
     </row>
     <row r="3">
@@ -790,13 +790,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>32837</v>
+        <v>31145</v>
       </c>
       <c r="C3" t="n">
-        <v>1071</v>
+        <v>1194</v>
       </c>
       <c r="D3" t="n">
-        <v>21783</v>
+        <v>23850</v>
       </c>
     </row>
     <row r="4">
@@ -804,13 +804,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>17265</v>
+        <v>16230</v>
       </c>
       <c r="C4" t="n">
-        <v>1029</v>
+        <v>1051</v>
       </c>
       <c r="D4" t="n">
-        <v>5735</v>
+        <v>6318</v>
       </c>
     </row>
     <row r="5">
@@ -818,13 +818,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9598</v>
+        <v>9114</v>
       </c>
       <c r="C5" t="n">
-        <v>550</v>
+        <v>583</v>
       </c>
       <c r="D5" t="n">
-        <v>1592</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="6">
@@ -832,13 +832,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>6335</v>
+        <v>6024</v>
       </c>
       <c r="C6" t="n">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="D6" t="n">
-        <v>899</v>
+        <v>894</v>
       </c>
     </row>
     <row r="7">
@@ -846,13 +846,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4999</v>
+        <v>4836</v>
       </c>
       <c r="C7" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="D7" t="n">
-        <v>707</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -860,13 +860,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3558</v>
+        <v>3748</v>
       </c>
       <c r="C8" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D8" t="n">
-        <v>579</v>
+        <v>556</v>
       </c>
     </row>
     <row r="9">
@@ -874,13 +874,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1216</v>
+        <v>1609</v>
       </c>
       <c r="C9" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D9" t="n">
-        <v>503</v>
+        <v>483</v>
       </c>
     </row>
     <row r="10">
@@ -888,13 +888,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>180</v>
+        <v>260</v>
       </c>
       <c r="C10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>425</v>
+        <v>419</v>
       </c>
     </row>
     <row r="11">
@@ -902,13 +902,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D11" t="n">
-        <v>353</v>
+        <v>366</v>
       </c>
     </row>
     <row r="12">
@@ -916,13 +916,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D12" t="n">
-        <v>289</v>
+        <v>303</v>
       </c>
     </row>
     <row r="13">
@@ -930,13 +930,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C13" t="n">
         <v>15</v>
       </c>
       <c r="D13" t="n">
-        <v>232</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14">
@@ -944,13 +944,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>182</v>
+        <v>212</v>
       </c>
     </row>
     <row r="15">
@@ -958,13 +958,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>130</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16">
@@ -972,13 +972,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>81</v>
+        <v>157</v>
       </c>
     </row>
     <row r="17">
@@ -986,13 +986,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18">
@@ -1000,13 +1000,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>88</v>
       </c>
     </row>
     <row r="19">
@@ -1014,13 +1014,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
@@ -1028,13 +1028,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21">
@@ -1042,13 +1042,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1087,13 +1087,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>73137</v>
+        <v>68939</v>
       </c>
       <c r="C2" t="n">
-        <v>644</v>
+        <v>842</v>
       </c>
       <c r="D2" t="n">
-        <v>70758</v>
+        <v>84463</v>
       </c>
     </row>
     <row r="3">
@@ -1101,13 +1101,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>40483</v>
+        <v>37654</v>
       </c>
       <c r="C3" t="n">
-        <v>950</v>
+        <v>1078</v>
       </c>
       <c r="D3" t="n">
-        <v>22971</v>
+        <v>25169</v>
       </c>
     </row>
     <row r="4">
@@ -1115,13 +1115,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23391</v>
+        <v>21474</v>
       </c>
       <c r="C4" t="n">
-        <v>1014</v>
+        <v>1043</v>
       </c>
       <c r="D4" t="n">
-        <v>6022</v>
+        <v>6738</v>
       </c>
     </row>
     <row r="5">
@@ -1129,13 +1129,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12464</v>
+        <v>11533</v>
       </c>
       <c r="C5" t="n">
-        <v>612</v>
+        <v>641</v>
       </c>
       <c r="D5" t="n">
-        <v>1631</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="6">
@@ -1143,13 +1143,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7715</v>
+        <v>7247</v>
       </c>
       <c r="C6" t="n">
-        <v>256</v>
+        <v>282</v>
       </c>
       <c r="D6" t="n">
-        <v>901</v>
+        <v>916</v>
       </c>
     </row>
     <row r="7">
@@ -1157,13 +1157,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5467</v>
+        <v>5139</v>
       </c>
       <c r="C7" t="n">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="D7" t="n">
-        <v>701</v>
+        <v>655</v>
       </c>
     </row>
     <row r="8">
@@ -1171,13 +1171,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4051</v>
+        <v>4045</v>
       </c>
       <c r="C8" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D8" t="n">
-        <v>574</v>
+        <v>548</v>
       </c>
     </row>
     <row r="9">
@@ -1185,13 +1185,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2034</v>
+        <v>2470</v>
       </c>
       <c r="C9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D9" t="n">
-        <v>500</v>
+        <v>480</v>
       </c>
     </row>
     <row r="10">
@@ -1199,13 +1199,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>520</v>
+        <v>843</v>
       </c>
       <c r="C10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>417</v>
+        <v>412</v>
       </c>
     </row>
     <row r="11">
@@ -1213,13 +1213,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>94</v>
+        <v>140</v>
       </c>
       <c r="C11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D11" t="n">
-        <v>347</v>
+        <v>360</v>
       </c>
     </row>
     <row r="12">
@@ -1227,13 +1227,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D12" t="n">
-        <v>282</v>
+        <v>298</v>
       </c>
     </row>
     <row r="13">
@@ -1241,13 +1241,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C13" t="n">
         <v>15</v>
       </c>
       <c r="D13" t="n">
-        <v>224</v>
+        <v>256</v>
       </c>
     </row>
     <row r="14">
@@ -1255,13 +1255,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>171</v>
+        <v>209</v>
       </c>
     </row>
     <row r="15">
@@ -1269,13 +1269,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>119</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16">
@@ -1283,13 +1283,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>69</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17">
@@ -1297,13 +1297,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
         <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>30</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18">
@@ -1311,13 +1311,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19">
@@ -1325,13 +1325,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20">
@@ -1339,13 +1339,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21">
@@ -1353,13 +1353,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1398,13 +1398,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>83706</v>
+        <v>77595</v>
       </c>
       <c r="C2" t="n">
-        <v>473</v>
+        <v>631</v>
       </c>
       <c r="D2" t="n">
-        <v>80133</v>
+        <v>98015</v>
       </c>
     </row>
     <row r="3">
@@ -1412,13 +1412,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>48631</v>
+        <v>44077</v>
       </c>
       <c r="C3" t="n">
-        <v>853</v>
+        <v>977</v>
       </c>
       <c r="D3" t="n">
-        <v>23654</v>
+        <v>25898</v>
       </c>
     </row>
     <row r="4">
@@ -1426,13 +1426,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28390</v>
+        <v>25830</v>
       </c>
       <c r="C4" t="n">
-        <v>983</v>
+        <v>1016</v>
       </c>
       <c r="D4" t="n">
-        <v>6327</v>
+        <v>7176</v>
       </c>
     </row>
     <row r="5">
@@ -1440,13 +1440,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>16152</v>
+        <v>14582</v>
       </c>
       <c r="C5" t="n">
-        <v>653</v>
+        <v>673</v>
       </c>
       <c r="D5" t="n">
-        <v>1690</v>
+        <v>2148</v>
       </c>
     </row>
     <row r="6">
@@ -1454,13 +1454,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9520</v>
+        <v>8770</v>
       </c>
       <c r="C6" t="n">
-        <v>296</v>
+        <v>329</v>
       </c>
       <c r="D6" t="n">
-        <v>894</v>
+        <v>940</v>
       </c>
     </row>
     <row r="7">
@@ -1468,13 +1468,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6218</v>
+        <v>5711</v>
       </c>
       <c r="C7" t="n">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="D7" t="n">
-        <v>694</v>
+        <v>658</v>
       </c>
     </row>
     <row r="8">
@@ -1482,13 +1482,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4403</v>
+        <v>4277</v>
       </c>
       <c r="C8" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D8" t="n">
-        <v>568</v>
+        <v>540</v>
       </c>
     </row>
     <row r="9">
@@ -1496,13 +1496,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2625</v>
+        <v>2945</v>
       </c>
       <c r="C9" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D9" t="n">
-        <v>492</v>
+        <v>472</v>
       </c>
     </row>
     <row r="10">
@@ -1510,13 +1510,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>924</v>
+        <v>1440</v>
       </c>
       <c r="C10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>409</v>
+        <v>405</v>
       </c>
     </row>
     <row r="11">
@@ -1524,13 +1524,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>189</v>
+        <v>398</v>
       </c>
       <c r="C11" t="n">
         <v>22</v>
       </c>
       <c r="D11" t="n">
-        <v>341</v>
+        <v>354</v>
       </c>
     </row>
     <row r="12">
@@ -1538,13 +1538,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="C12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D12" t="n">
-        <v>274</v>
+        <v>293</v>
       </c>
     </row>
     <row r="13">
@@ -1552,13 +1552,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C13" t="n">
         <v>15</v>
       </c>
       <c r="D13" t="n">
-        <v>215</v>
+        <v>252</v>
       </c>
     </row>
     <row r="14">
@@ -1566,13 +1566,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>160</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15">
@@ -1580,13 +1580,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>108</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16">
@@ -1594,13 +1594,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>58</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17">
@@ -1608,13 +1608,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
+        <v>13</v>
+      </c>
+      <c r="C17" t="n">
         <v>8</v>
       </c>
-      <c r="C17" t="n">
-        <v>7</v>
-      </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -1622,13 +1622,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19">
@@ -1636,13 +1636,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20">
@@ -1650,13 +1650,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21">
@@ -1664,13 +1664,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1709,13 +1709,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>89398</v>
+        <v>81145</v>
       </c>
       <c r="C2" t="n">
-        <v>373</v>
+        <v>511</v>
       </c>
       <c r="D2" t="n">
-        <v>71073</v>
+        <v>86850</v>
       </c>
     </row>
     <row r="3">
@@ -1723,13 +1723,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>54358</v>
+        <v>48588</v>
       </c>
       <c r="C3" t="n">
-        <v>760</v>
+        <v>877</v>
       </c>
       <c r="D3" t="n">
-        <v>24176</v>
+        <v>27252</v>
       </c>
     </row>
     <row r="4">
@@ -1737,13 +1737,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33191</v>
+        <v>29223</v>
       </c>
       <c r="C4" t="n">
-        <v>945</v>
+        <v>979</v>
       </c>
       <c r="D4" t="n">
-        <v>6467</v>
+        <v>7428</v>
       </c>
     </row>
     <row r="5">
@@ -1751,13 +1751,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19690</v>
+        <v>17363</v>
       </c>
       <c r="C5" t="n">
-        <v>671</v>
+        <v>688</v>
       </c>
       <c r="D5" t="n">
-        <v>1700</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="6">
@@ -1765,13 +1765,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11572</v>
+        <v>10574</v>
       </c>
       <c r="C6" t="n">
-        <v>332</v>
+        <v>367</v>
       </c>
       <c r="D6" t="n">
-        <v>879</v>
+        <v>955</v>
       </c>
     </row>
     <row r="7">
@@ -1779,13 +1779,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7134</v>
+        <v>6488</v>
       </c>
       <c r="C7" t="n">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="D7" t="n">
-        <v>687</v>
+        <v>653</v>
       </c>
     </row>
     <row r="8">
@@ -1793,13 +1793,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4841</v>
+        <v>4521</v>
       </c>
       <c r="C8" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="D8" t="n">
-        <v>562</v>
+        <v>532</v>
       </c>
     </row>
     <row r="9">
@@ -1807,13 +1807,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2998</v>
+        <v>3255</v>
       </c>
       <c r="C9" t="n">
         <v>37</v>
       </c>
       <c r="D9" t="n">
-        <v>484</v>
+        <v>464</v>
       </c>
     </row>
     <row r="10">
@@ -1821,13 +1821,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1289</v>
+        <v>1858</v>
       </c>
       <c r="C10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>404</v>
+        <v>398</v>
       </c>
     </row>
     <row r="11">
@@ -1835,13 +1835,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>319</v>
+        <v>721</v>
       </c>
       <c r="C11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D11" t="n">
-        <v>331</v>
+        <v>351</v>
       </c>
     </row>
     <row r="12">
@@ -1849,13 +1849,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>74</v>
+        <v>173</v>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>266</v>
+        <v>288</v>
       </c>
     </row>
     <row r="13">
@@ -1863,13 +1863,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C13" t="n">
         <v>15</v>
       </c>
       <c r="D13" t="n">
-        <v>206</v>
+        <v>247</v>
       </c>
     </row>
     <row r="14">
@@ -1877,13 +1877,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>150</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15">
@@ -1891,13 +1891,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>95</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16">
@@ -1905,13 +1905,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>48</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17">
@@ -1919,13 +1919,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18">
@@ -1933,13 +1933,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19">
@@ -1947,13 +1947,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20">
@@ -1961,13 +1961,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21">
@@ -1975,13 +1975,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2020,13 +2020,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>95829</v>
+        <v>85647</v>
       </c>
       <c r="C2" t="n">
-        <v>291</v>
+        <v>407</v>
       </c>
       <c r="D2" t="n">
-        <v>76273</v>
+        <v>95394</v>
       </c>
     </row>
     <row r="3">
@@ -2034,13 +2034,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>57614</v>
+        <v>50804</v>
       </c>
       <c r="C3" t="n">
-        <v>680</v>
+        <v>789</v>
       </c>
       <c r="D3" t="n">
-        <v>24450</v>
+        <v>27461</v>
       </c>
     </row>
     <row r="4">
@@ -2048,13 +2048,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36701</v>
+        <v>31746</v>
       </c>
       <c r="C4" t="n">
-        <v>894</v>
+        <v>928</v>
       </c>
       <c r="D4" t="n">
-        <v>6610</v>
+        <v>7701</v>
       </c>
     </row>
     <row r="5">
@@ -2062,13 +2062,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22672</v>
+        <v>19817</v>
       </c>
       <c r="C5" t="n">
-        <v>685</v>
+        <v>700</v>
       </c>
       <c r="D5" t="n">
-        <v>1711</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="6">
@@ -2076,13 +2076,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13820</v>
+        <v>12189</v>
       </c>
       <c r="C6" t="n">
-        <v>360</v>
+        <v>392</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>971</v>
       </c>
     </row>
     <row r="7">
@@ -2090,13 +2090,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8101</v>
+        <v>7414</v>
       </c>
       <c r="C7" t="n">
-        <v>141</v>
+        <v>173</v>
       </c>
       <c r="D7" t="n">
-        <v>680</v>
+        <v>648</v>
       </c>
     </row>
     <row r="8">
@@ -2104,13 +2104,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5266</v>
+        <v>4855</v>
       </c>
       <c r="C8" t="n">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="D8" t="n">
-        <v>556</v>
+        <v>524</v>
       </c>
     </row>
     <row r="9">
@@ -2118,13 +2118,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3334</v>
+        <v>3435</v>
       </c>
       <c r="C9" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D9" t="n">
-        <v>480</v>
+        <v>461</v>
       </c>
     </row>
     <row r="10">
@@ -2132,13 +2132,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1554</v>
+        <v>2177</v>
       </c>
       <c r="C10" t="n">
         <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="11">
@@ -2146,13 +2146,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>452</v>
+        <v>998</v>
       </c>
       <c r="C11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D11" t="n">
-        <v>324</v>
+        <v>344</v>
       </c>
     </row>
     <row r="12">
@@ -2160,13 +2160,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>97</v>
+        <v>313</v>
       </c>
       <c r="C12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D12" t="n">
-        <v>255</v>
+        <v>283</v>
       </c>
     </row>
     <row r="13">
@@ -2174,13 +2174,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="C13" t="n">
         <v>15</v>
       </c>
       <c r="D13" t="n">
-        <v>198</v>
+        <v>242</v>
       </c>
     </row>
     <row r="14">
@@ -2188,13 +2188,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>138</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15">
@@ -2202,13 +2202,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16">
@@ -2216,13 +2216,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>39</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17">
@@ -2230,13 +2230,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18">
@@ -2244,13 +2244,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19">
@@ -2258,13 +2258,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20">
@@ -2272,13 +2272,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21">
@@ -2286,13 +2286,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2331,13 +2331,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>95443</v>
+        <v>83624</v>
       </c>
       <c r="C2" t="n">
-        <v>263</v>
+        <v>373</v>
       </c>
       <c r="D2" t="n">
-        <v>61628</v>
+        <v>77298</v>
       </c>
     </row>
     <row r="3">
@@ -2345,13 +2345,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>60056</v>
+        <v>52116</v>
       </c>
       <c r="C3" t="n">
-        <v>606</v>
+        <v>709</v>
       </c>
       <c r="D3" t="n">
-        <v>24833</v>
+        <v>27861</v>
       </c>
     </row>
     <row r="4">
@@ -2359,13 +2359,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38799</v>
+        <v>33001</v>
       </c>
       <c r="C4" t="n">
-        <v>852</v>
+        <v>885</v>
       </c>
       <c r="D4" t="n">
-        <v>6768</v>
+        <v>7962</v>
       </c>
     </row>
     <row r="5">
@@ -2373,13 +2373,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25086</v>
+        <v>21464</v>
       </c>
       <c r="C5" t="n">
-        <v>682</v>
+        <v>693</v>
       </c>
       <c r="D5" t="n">
-        <v>1706</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="6">
@@ -2387,13 +2387,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15688</v>
+        <v>13701</v>
       </c>
       <c r="C6" t="n">
-        <v>384</v>
+        <v>412</v>
       </c>
       <c r="D6" t="n">
-        <v>856</v>
+        <v>997</v>
       </c>
     </row>
     <row r="7">
@@ -2401,13 +2401,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9264</v>
+        <v>8330</v>
       </c>
       <c r="C7" t="n">
-        <v>153</v>
+        <v>192</v>
       </c>
       <c r="D7" t="n">
-        <v>672</v>
+        <v>641</v>
       </c>
     </row>
     <row r="8">
@@ -2415,13 +2415,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5640</v>
+        <v>5263</v>
       </c>
       <c r="C8" t="n">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="D8" t="n">
-        <v>549</v>
+        <v>515</v>
       </c>
     </row>
     <row r="9">
@@ -2429,13 +2429,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3609</v>
+        <v>3599</v>
       </c>
       <c r="C9" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D9" t="n">
-        <v>471</v>
+        <v>453</v>
       </c>
     </row>
     <row r="10">
@@ -2443,13 +2443,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1756</v>
+        <v>2368</v>
       </c>
       <c r="C10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="11">
@@ -2457,13 +2457,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>560</v>
+        <v>1245</v>
       </c>
       <c r="C11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D11" t="n">
-        <v>316</v>
+        <v>338</v>
       </c>
     </row>
     <row r="12">
@@ -2471,13 +2471,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>117</v>
+        <v>456</v>
       </c>
       <c r="C12" t="n">
         <v>16</v>
       </c>
       <c r="D12" t="n">
-        <v>247</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13">
@@ -2485,13 +2485,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>39</v>
+        <v>127</v>
       </c>
       <c r="C13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D13" t="n">
-        <v>187</v>
+        <v>237</v>
       </c>
     </row>
     <row r="14">
@@ -2499,13 +2499,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="C14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>126</v>
+        <v>196</v>
       </c>
     </row>
     <row r="15">
@@ -2513,13 +2513,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>72</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16">
@@ -2527,13 +2527,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C16" t="n">
         <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>30</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17">
@@ -2541,13 +2541,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18">
@@ -2555,13 +2555,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19">
@@ -2569,13 +2569,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -2583,13 +2583,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21">
@@ -2597,13 +2597,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2642,13 +2642,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>76979</v>
+        <v>70735</v>
       </c>
       <c r="C2" t="n">
-        <v>280</v>
+        <v>380</v>
       </c>
       <c r="D2" t="n">
-        <v>51687</v>
+        <v>64246</v>
       </c>
     </row>
     <row r="3">
@@ -2656,13 +2656,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>71725</v>
+        <v>58845</v>
       </c>
       <c r="C3" t="n">
-        <v>863</v>
+        <v>964</v>
       </c>
       <c r="D3" t="n">
-        <v>23209</v>
+        <v>26250</v>
       </c>
     </row>
     <row r="4">
@@ -2670,13 +2670,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35410</v>
+        <v>29954</v>
       </c>
       <c r="C4" t="n">
-        <v>1048</v>
+        <v>1063</v>
       </c>
       <c r="D4" t="n">
-        <v>5594</v>
+        <v>6830</v>
       </c>
     </row>
     <row r="5">
@@ -2684,13 +2684,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>14495</v>
+        <v>12659</v>
       </c>
       <c r="C5" t="n">
-        <v>448</v>
+        <v>490</v>
       </c>
       <c r="D5" t="n">
-        <v>1524</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="6">
@@ -2698,13 +2698,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8559</v>
+        <v>7696</v>
       </c>
       <c r="C6" t="n">
-        <v>149</v>
+        <v>188</v>
       </c>
       <c r="D6" t="n">
-        <v>759</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -2712,13 +2712,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5211</v>
+        <v>4863</v>
       </c>
       <c r="C7" t="n">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>504</v>
       </c>
     </row>
     <row r="8">
@@ -2726,13 +2726,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3334</v>
+        <v>3325</v>
       </c>
       <c r="C8" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D8" t="n">
-        <v>461</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9">
@@ -2740,13 +2740,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1622</v>
+        <v>2188</v>
       </c>
       <c r="C9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10">
@@ -2754,13 +2754,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>517</v>
+        <v>1150</v>
       </c>
       <c r="C10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D10" t="n">
-        <v>309</v>
+        <v>331</v>
       </c>
     </row>
     <row r="11">
@@ -2768,13 +2768,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>108</v>
+        <v>421</v>
       </c>
       <c r="C11" t="n">
         <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>242</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12">
@@ -2782,13 +2782,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>117</v>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D12" t="n">
-        <v>183</v>
+        <v>232</v>
       </c>
     </row>
     <row r="13">
@@ -2796,13 +2796,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14">
@@ -2810,13 +2810,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>70</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15">
@@ -2824,13 +2824,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C15" t="n">
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>29</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16">
@@ -2838,13 +2838,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17">
@@ -2852,13 +2852,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -2866,13 +2866,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -2880,13 +2880,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20">
@@ -2894,13 +2894,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -2953,13 +2953,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9795</v>
+        <v>9915</v>
       </c>
       <c r="C2" t="n">
-        <v>3361</v>
+        <v>3573</v>
       </c>
       <c r="D2" t="n">
-        <v>16365</v>
+        <v>17139</v>
       </c>
     </row>
     <row r="3">
@@ -2967,13 +2967,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C3" t="n">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D3" t="n">
-        <v>7876</v>
+        <v>7767</v>
       </c>
     </row>
     <row r="4">
@@ -2981,13 +2981,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="C4" t="n">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D4" t="n">
-        <v>6279</v>
+        <v>6314</v>
       </c>
     </row>
     <row r="5">
@@ -2995,13 +2995,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="C5" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D5" t="n">
-        <v>1593</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="6">
@@ -3009,13 +3009,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="C6" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D6" t="n">
-        <v>1400</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="7">
@@ -3023,13 +3023,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="C7" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D7" t="n">
-        <v>1298</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="8">
@@ -3037,13 +3037,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C8" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D8" t="n">
-        <v>1167</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="9">
@@ -3051,13 +3051,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C9" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D9" t="n">
-        <v>1074</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="10">
@@ -3065,13 +3065,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C10" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>934</v>
+        <v>940</v>
       </c>
     </row>
     <row r="11">
@@ -3079,13 +3079,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C11" t="n">
         <v>63</v>
       </c>
       <c r="D11" t="n">
-        <v>837</v>
+        <v>833</v>
       </c>
     </row>
     <row r="12">
@@ -3093,13 +3093,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C12" t="n">
         <v>55</v>
       </c>
       <c r="D12" t="n">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="13">
@@ -3107,13 +3107,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C13" t="n">
         <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>606</v>
+        <v>609</v>
       </c>
     </row>
     <row r="14">
@@ -3121,13 +3121,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="15">
@@ -3135,13 +3135,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="16">
@@ -3149,13 +3149,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C16" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>366</v>
+        <v>389</v>
       </c>
     </row>
     <row r="17">
@@ -3163,13 +3163,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C17" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D17" t="n">
-        <v>277</v>
+        <v>289</v>
       </c>
     </row>
     <row r="18">
@@ -3177,13 +3177,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C18" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D18" t="n">
-        <v>209</v>
+        <v>224</v>
       </c>
     </row>
     <row r="19">
@@ -3191,13 +3191,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C19" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D19" t="n">
-        <v>138</v>
+        <v>161</v>
       </c>
     </row>
     <row r="20">
@@ -3205,13 +3205,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="D20" t="n">
-        <v>54</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21">
@@ -3219,13 +3219,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="C21" t="n">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3264,13 +3264,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18940</v>
+        <v>19402</v>
       </c>
       <c r="C2" t="n">
-        <v>3283</v>
+        <v>3522</v>
       </c>
       <c r="D2" t="n">
-        <v>56701</v>
+        <v>60635</v>
       </c>
     </row>
     <row r="3">
@@ -3278,13 +3278,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4467</v>
+        <v>4448</v>
       </c>
       <c r="C3" t="n">
-        <v>556</v>
+        <v>584</v>
       </c>
       <c r="D3" t="n">
-        <v>6495</v>
+        <v>6447</v>
       </c>
     </row>
     <row r="4">
@@ -3292,13 +3292,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C4" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
-        <v>4291</v>
+        <v>4349</v>
       </c>
     </row>
     <row r="5">
@@ -3306,13 +3306,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C5" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D5" t="n">
-        <v>1031</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="6">
@@ -3320,13 +3320,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C6" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D6" t="n">
-        <v>812</v>
+        <v>792</v>
       </c>
     </row>
     <row r="7">
@@ -3334,13 +3334,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
         <v>43</v>
       </c>
       <c r="D7" t="n">
-        <v>708</v>
+        <v>693</v>
       </c>
     </row>
     <row r="8">
@@ -3348,13 +3348,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D8" t="n">
-        <v>609</v>
+        <v>598</v>
       </c>
     </row>
     <row r="9">
@@ -3362,13 +3362,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C9" t="n">
         <v>31</v>
       </c>
       <c r="D9" t="n">
-        <v>543</v>
+        <v>529</v>
       </c>
     </row>
     <row r="10">
@@ -3376,13 +3376,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>455</v>
+        <v>463</v>
       </c>
     </row>
     <row r="11">
@@ -3393,10 +3393,10 @@
         <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D11" t="n">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="12">
@@ -3404,7 +3404,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
         <v>19</v>
@@ -3418,13 +3418,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" t="n">
         <v>15</v>
       </c>
       <c r="D13" t="n">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="14">
@@ -3432,13 +3432,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="15">
@@ -3446,13 +3446,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="16">
@@ -3460,13 +3460,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D16" t="n">
-        <v>154</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17">
@@ -3477,10 +3477,10 @@
         <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D17" t="n">
-        <v>115</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18">
@@ -3491,10 +3491,10 @@
         <v>14</v>
       </c>
       <c r="C18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D18" t="n">
-        <v>83</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19">
@@ -3502,13 +3502,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
+        <v>12</v>
+      </c>
+      <c r="C19" t="n">
         <v>13</v>
       </c>
-      <c r="C19" t="n">
-        <v>16</v>
-      </c>
       <c r="D19" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20">
@@ -3519,10 +3519,10 @@
         <v>12</v>
       </c>
       <c r="C20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D20" t="n">
-        <v>13</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21">
@@ -3530,13 +3530,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3575,13 +3575,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6880</v>
+        <v>7445</v>
       </c>
       <c r="C2" t="n">
-        <v>2333</v>
+        <v>2517</v>
       </c>
       <c r="D2" t="n">
-        <v>54397</v>
+        <v>58699</v>
       </c>
     </row>
     <row r="3">
@@ -3589,13 +3589,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14055</v>
+        <v>14231</v>
       </c>
       <c r="C3" t="n">
-        <v>1104</v>
+        <v>1170</v>
       </c>
       <c r="D3" t="n">
-        <v>8645</v>
+        <v>8728</v>
       </c>
     </row>
     <row r="4">
@@ -3603,13 +3603,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3397</v>
+        <v>3381</v>
       </c>
       <c r="C4" t="n">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="D4" t="n">
-        <v>4266</v>
+        <v>4295</v>
       </c>
     </row>
     <row r="5">
@@ -3617,13 +3617,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C5" t="n">
         <v>81</v>
       </c>
       <c r="D5" t="n">
-        <v>1124</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="6">
@@ -3631,13 +3631,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C6" t="n">
         <v>54</v>
       </c>
       <c r="D6" t="n">
-        <v>824</v>
+        <v>793</v>
       </c>
     </row>
     <row r="7">
@@ -3645,13 +3645,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C7" t="n">
         <v>44</v>
       </c>
       <c r="D7" t="n">
-        <v>712</v>
+        <v>684</v>
       </c>
     </row>
     <row r="8">
@@ -3659,13 +3659,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D8" t="n">
-        <v>605</v>
+        <v>597</v>
       </c>
     </row>
     <row r="9">
@@ -3673,13 +3673,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C9" t="n">
         <v>31</v>
       </c>
       <c r="D9" t="n">
-        <v>536</v>
+        <v>521</v>
       </c>
     </row>
     <row r="10">
@@ -3690,10 +3690,10 @@
         <v>51</v>
       </c>
       <c r="C10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="11">
@@ -3704,10 +3704,10 @@
         <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D11" t="n">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="12">
@@ -3715,13 +3715,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
         <v>19</v>
       </c>
       <c r="D12" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="13">
@@ -3729,13 +3729,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C13" t="n">
         <v>15</v>
       </c>
       <c r="D13" t="n">
-        <v>272</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14">
@@ -3743,13 +3743,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>225</v>
+        <v>230</v>
       </c>
     </row>
     <row r="15">
@@ -3757,13 +3757,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>188</v>
+        <v>198</v>
       </c>
     </row>
     <row r="16">
@@ -3771,13 +3771,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D16" t="n">
-        <v>145</v>
+        <v>171</v>
       </c>
     </row>
     <row r="17">
@@ -3785,13 +3785,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>106</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18">
@@ -3799,13 +3799,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D18" t="n">
-        <v>71</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19">
@@ -3816,10 +3816,10 @@
         <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
-        <v>33</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20">
@@ -3827,13 +3827,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21">
@@ -3841,13 +3841,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -3886,13 +3886,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8356</v>
+        <v>9149</v>
       </c>
       <c r="C2" t="n">
-        <v>2684</v>
+        <v>2999</v>
       </c>
       <c r="D2" t="n">
-        <v>73914</v>
+        <v>81764</v>
       </c>
     </row>
     <row r="3">
@@ -3900,13 +3900,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6335</v>
+        <v>6757</v>
       </c>
       <c r="C3" t="n">
-        <v>1288</v>
+        <v>1354</v>
       </c>
       <c r="D3" t="n">
-        <v>10495</v>
+        <v>10693</v>
       </c>
     </row>
     <row r="4">
@@ -3914,13 +3914,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11000</v>
+        <v>10980</v>
       </c>
       <c r="C4" t="n">
-        <v>441</v>
+        <v>458</v>
       </c>
       <c r="D4" t="n">
-        <v>4346</v>
+        <v>4378</v>
       </c>
     </row>
     <row r="5">
@@ -3928,13 +3928,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2446</v>
+        <v>2460</v>
       </c>
       <c r="C5" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="D5" t="n">
-        <v>1210</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="6">
@@ -3942,13 +3942,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="C6" t="n">
         <v>59</v>
       </c>
       <c r="D6" t="n">
-        <v>838</v>
+        <v>802</v>
       </c>
     </row>
     <row r="7">
@@ -3956,13 +3956,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C7" t="n">
         <v>45</v>
       </c>
       <c r="D7" t="n">
-        <v>716</v>
+        <v>676</v>
       </c>
     </row>
     <row r="8">
@@ -3970,13 +3970,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C8" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D8" t="n">
-        <v>601</v>
+        <v>596</v>
       </c>
     </row>
     <row r="9">
@@ -3984,13 +3984,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D9" t="n">
-        <v>530</v>
+        <v>514</v>
       </c>
     </row>
     <row r="10">
@@ -3998,13 +3998,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="11">
@@ -4012,13 +4012,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D11" t="n">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="12">
@@ -4026,13 +4026,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C12" t="n">
         <v>19</v>
       </c>
       <c r="D12" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="13">
@@ -4040,13 +4040,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C13" t="n">
         <v>15</v>
       </c>
       <c r="D13" t="n">
-        <v>268</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14">
@@ -4054,13 +4054,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>219</v>
+        <v>227</v>
       </c>
     </row>
     <row r="15">
@@ -4068,13 +4068,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>180</v>
+        <v>195</v>
       </c>
     </row>
     <row r="16">
@@ -4082,13 +4082,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D16" t="n">
-        <v>135</v>
+        <v>168</v>
       </c>
     </row>
     <row r="17">
@@ -4096,13 +4096,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>96</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18">
@@ -4110,13 +4110,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C18" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19">
@@ -4127,10 +4127,10 @@
         <v>11</v>
       </c>
       <c r="C19" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>22</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20">
@@ -4138,13 +4138,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21">
@@ -4152,13 +4152,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -4197,13 +4197,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>17142</v>
+        <v>17798</v>
       </c>
       <c r="C2" t="n">
-        <v>1902</v>
+        <v>2178</v>
       </c>
       <c r="D2" t="n">
-        <v>69939</v>
+        <v>78211</v>
       </c>
     </row>
     <row r="3">
@@ -4211,13 +4211,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6625</v>
+        <v>7069</v>
       </c>
       <c r="C3" t="n">
-        <v>1485</v>
+        <v>1574</v>
       </c>
       <c r="D3" t="n">
-        <v>13119</v>
+        <v>13574</v>
       </c>
     </row>
     <row r="4">
@@ -4225,13 +4225,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>6368</v>
+        <v>6519</v>
       </c>
       <c r="C4" t="n">
-        <v>635</v>
+        <v>654</v>
       </c>
       <c r="D4" t="n">
-        <v>4509</v>
+        <v>4566</v>
       </c>
     </row>
     <row r="5">
@@ -4239,13 +4239,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>8111</v>
+        <v>8148</v>
       </c>
       <c r="C5" t="n">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="D5" t="n">
-        <v>1305</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="6">
@@ -4253,13 +4253,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1761</v>
+        <v>1811</v>
       </c>
       <c r="C6" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D6" t="n">
-        <v>843</v>
+        <v>818</v>
       </c>
     </row>
     <row r="7">
@@ -4267,13 +4267,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="C7" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D7" t="n">
-        <v>720</v>
+        <v>676</v>
       </c>
     </row>
     <row r="8">
@@ -4281,13 +4281,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C8" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D8" t="n">
-        <v>597</v>
+        <v>588</v>
       </c>
     </row>
     <row r="9">
@@ -4295,13 +4295,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>524</v>
+        <v>507</v>
       </c>
     </row>
     <row r="10">
@@ -4309,13 +4309,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>448</v>
+        <v>444</v>
       </c>
     </row>
     <row r="11">
@@ -4326,10 +4326,10 @@
         <v>48</v>
       </c>
       <c r="C11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D11" t="n">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="12">
@@ -4337,13 +4337,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C12" t="n">
         <v>19</v>
       </c>
       <c r="D12" t="n">
-        <v>312</v>
+        <v>321</v>
       </c>
     </row>
     <row r="13">
@@ -4351,13 +4351,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C13" t="n">
         <v>15</v>
       </c>
       <c r="D13" t="n">
-        <v>264</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14">
@@ -4365,13 +4365,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>212</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15">
@@ -4379,13 +4379,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>171</v>
+        <v>192</v>
       </c>
     </row>
     <row r="16">
@@ -4393,13 +4393,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D16" t="n">
-        <v>125</v>
+        <v>167</v>
       </c>
     </row>
     <row r="17">
@@ -4407,13 +4407,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>85</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18">
@@ -4421,13 +4421,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>46</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19">
@@ -4435,13 +4435,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
         <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>14</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20">
@@ -4449,13 +4449,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21">
@@ -4463,13 +4463,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -4508,13 +4508,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21853</v>
+        <v>22126</v>
       </c>
       <c r="C2" t="n">
-        <v>1502</v>
+        <v>1764</v>
       </c>
       <c r="D2" t="n">
-        <v>76029</v>
+        <v>86656</v>
       </c>
     </row>
     <row r="3">
@@ -4522,13 +4522,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12535</v>
+        <v>12677</v>
       </c>
       <c r="C3" t="n">
-        <v>1463</v>
+        <v>1566</v>
       </c>
       <c r="D3" t="n">
-        <v>15321</v>
+        <v>16003</v>
       </c>
     </row>
     <row r="4">
@@ -4536,13 +4536,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>5822</v>
+        <v>6100</v>
       </c>
       <c r="C4" t="n">
-        <v>817</v>
+        <v>839</v>
       </c>
       <c r="D4" t="n">
-        <v>4785</v>
+        <v>4902</v>
       </c>
     </row>
     <row r="5">
@@ -4550,13 +4550,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6180</v>
+        <v>6139</v>
       </c>
       <c r="C5" t="n">
-        <v>273</v>
+        <v>294</v>
       </c>
       <c r="D5" t="n">
-        <v>1400</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="6">
@@ -4564,13 +4564,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>6050</v>
+        <v>6156</v>
       </c>
       <c r="C6" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D6" t="n">
-        <v>849</v>
+        <v>833</v>
       </c>
     </row>
     <row r="7">
@@ -4578,13 +4578,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1151</v>
+        <v>1258</v>
       </c>
       <c r="C7" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D7" t="n">
-        <v>724</v>
+        <v>669</v>
       </c>
     </row>
     <row r="8">
@@ -4592,13 +4592,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D8" t="n">
-        <v>593</v>
+        <v>580</v>
       </c>
     </row>
     <row r="9">
@@ -4606,13 +4606,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>518</v>
+        <v>500</v>
       </c>
     </row>
     <row r="10">
@@ -4620,13 +4620,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>445</v>
+        <v>438</v>
       </c>
     </row>
     <row r="11">
@@ -4634,13 +4634,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D11" t="n">
-        <v>372</v>
+        <v>380</v>
       </c>
     </row>
     <row r="12">
@@ -4654,7 +4654,7 @@
         <v>19</v>
       </c>
       <c r="D12" t="n">
-        <v>307</v>
+        <v>316</v>
       </c>
     </row>
     <row r="13">
@@ -4662,13 +4662,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C13" t="n">
         <v>15</v>
       </c>
       <c r="D13" t="n">
-        <v>256</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14">
@@ -4676,13 +4676,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>205</v>
+        <v>221</v>
       </c>
     </row>
     <row r="15">
@@ -4690,13 +4690,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>162</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16">
@@ -4704,13 +4704,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D16" t="n">
-        <v>115</v>
+        <v>166</v>
       </c>
     </row>
     <row r="17">
@@ -4718,13 +4718,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>73</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18">
@@ -4735,10 +4735,10 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>34</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19">
@@ -4746,13 +4746,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20">
@@ -4760,13 +4760,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21">
@@ -4774,13 +4774,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -4819,13 +4819,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>33385</v>
+        <v>32923</v>
       </c>
       <c r="C2" t="n">
-        <v>1100</v>
+        <v>1324</v>
       </c>
       <c r="D2" t="n">
-        <v>92556</v>
+        <v>107211</v>
       </c>
     </row>
     <row r="3">
@@ -4833,13 +4833,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16160</v>
+        <v>16044</v>
       </c>
       <c r="C3" t="n">
-        <v>1369</v>
+        <v>1482</v>
       </c>
       <c r="D3" t="n">
-        <v>17160</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="4">
@@ -4847,13 +4847,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>9619</v>
+        <v>9559</v>
       </c>
       <c r="C4" t="n">
-        <v>942</v>
+        <v>974</v>
       </c>
       <c r="D4" t="n">
-        <v>5044</v>
+        <v>5392</v>
       </c>
     </row>
     <row r="5">
@@ -4861,13 +4861,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>5383</v>
+        <v>5490</v>
       </c>
       <c r="C5" t="n">
-        <v>376</v>
+        <v>397</v>
       </c>
       <c r="D5" t="n">
-        <v>1454</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="6">
@@ -4875,13 +4875,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5953</v>
+        <v>5790</v>
       </c>
       <c r="C6" t="n">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="D6" t="n">
-        <v>865</v>
+        <v>853</v>
       </c>
     </row>
     <row r="7">
@@ -4889,13 +4889,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4059</v>
+        <v>4308</v>
       </c>
       <c r="C7" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D7" t="n">
-        <v>719</v>
+        <v>663</v>
       </c>
     </row>
     <row r="8">
@@ -4903,13 +4903,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>673</v>
+        <v>802</v>
       </c>
       <c r="C8" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D8" t="n">
-        <v>589</v>
+        <v>572</v>
       </c>
     </row>
     <row r="9">
@@ -4917,13 +4917,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D9" t="n">
-        <v>517</v>
+        <v>498</v>
       </c>
     </row>
     <row r="10">
@@ -4931,13 +4931,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>437</v>
+        <v>431</v>
       </c>
     </row>
     <row r="11">
@@ -4945,13 +4945,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D11" t="n">
-        <v>367</v>
+        <v>374</v>
       </c>
     </row>
     <row r="12">
@@ -4965,7 +4965,7 @@
         <v>19</v>
       </c>
       <c r="D12" t="n">
-        <v>301</v>
+        <v>312</v>
       </c>
     </row>
     <row r="13">
@@ -4973,13 +4973,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C13" t="n">
         <v>15</v>
       </c>
       <c r="D13" t="n">
-        <v>248</v>
+        <v>266</v>
       </c>
     </row>
     <row r="14">
@@ -4987,13 +4987,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>197</v>
+        <v>218</v>
       </c>
     </row>
     <row r="15">
@@ -5001,13 +5001,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>153</v>
+        <v>188</v>
       </c>
     </row>
     <row r="16">
@@ -5018,10 +5018,10 @@
         <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D16" t="n">
-        <v>104</v>
+        <v>163</v>
       </c>
     </row>
     <row r="17">
@@ -5029,13 +5029,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>61</v>
+        <v>120</v>
       </c>
     </row>
     <row r="18">
@@ -5043,13 +5043,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>24</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19">
@@ -5057,13 +5057,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20">
@@ -5071,13 +5071,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21">
@@ -5085,13 +5085,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5130,13 +5130,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>48227</v>
+        <v>47330</v>
       </c>
       <c r="C2" t="n">
-        <v>790</v>
+        <v>973</v>
       </c>
       <c r="D2" t="n">
-        <v>94936</v>
+        <v>111729</v>
       </c>
     </row>
     <row r="3">
@@ -5144,13 +5144,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23481</v>
+        <v>22537</v>
       </c>
       <c r="C3" t="n">
-        <v>1231</v>
+        <v>1346</v>
       </c>
       <c r="D3" t="n">
-        <v>19516</v>
+        <v>21251</v>
       </c>
     </row>
     <row r="4">
@@ -5158,13 +5158,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12591</v>
+        <v>12174</v>
       </c>
       <c r="C4" t="n">
-        <v>1008</v>
+        <v>1037</v>
       </c>
       <c r="D4" t="n">
-        <v>5355</v>
+        <v>5810</v>
       </c>
     </row>
     <row r="5">
@@ -5172,13 +5172,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>7395</v>
+        <v>7262</v>
       </c>
       <c r="C5" t="n">
-        <v>467</v>
+        <v>501</v>
       </c>
       <c r="D5" t="n">
-        <v>1513</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="6">
@@ -5186,13 +5186,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5378</v>
+        <v>5274</v>
       </c>
       <c r="C6" t="n">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="D6" t="n">
-        <v>889</v>
+        <v>876</v>
       </c>
     </row>
     <row r="7">
@@ -5200,13 +5200,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5005</v>
+        <v>4936</v>
       </c>
       <c r="C7" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="D7" t="n">
-        <v>713</v>
+        <v>665</v>
       </c>
     </row>
     <row r="8">
@@ -5214,13 +5214,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2404</v>
+        <v>2764</v>
       </c>
       <c r="C8" t="n">
         <v>43</v>
       </c>
       <c r="D8" t="n">
-        <v>584</v>
+        <v>564</v>
       </c>
     </row>
     <row r="9">
@@ -5228,13 +5228,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>358</v>
+        <v>471</v>
       </c>
       <c r="C9" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D9" t="n">
-        <v>510</v>
+        <v>490</v>
       </c>
     </row>
     <row r="10">
@@ -5242,13 +5242,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="11">
@@ -5256,13 +5256,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D11" t="n">
-        <v>362</v>
+        <v>368</v>
       </c>
     </row>
     <row r="12">
@@ -5276,7 +5276,7 @@
         <v>19</v>
       </c>
       <c r="D12" t="n">
-        <v>295</v>
+        <v>308</v>
       </c>
     </row>
     <row r="13">
@@ -5284,13 +5284,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C13" t="n">
         <v>15</v>
       </c>
       <c r="D13" t="n">
-        <v>240</v>
+        <v>265</v>
       </c>
     </row>
     <row r="14">
@@ -5298,13 +5298,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D14" t="n">
-        <v>190</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15">
@@ -5312,13 +5312,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>141</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16">
@@ -5329,10 +5329,10 @@
         <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D16" t="n">
-        <v>93</v>
+        <v>160</v>
       </c>
     </row>
     <row r="17">
@@ -5343,10 +5343,10 @@
         <v>13</v>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18">
@@ -5354,13 +5354,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
         <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>17</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19">
@@ -5368,13 +5368,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20">
@@ -5382,13 +5382,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21">
@@ -5396,13 +5396,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
